--- a/Data/Parabolic Trough.xlsx
+++ b/Data/Parabolic Trough.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Benders-Decomposition/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E07EE4-5E49-7144-AB60-2A0A326ACDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D78836-E27B-974C-9C2D-85FD63E7F1DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20060" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
   </bookViews>
   <sheets>
     <sheet name="Initial values" sheetId="7" r:id="rId1"/>
@@ -145,8 +145,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -510,14 +511,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{690F904E-92CB-A441-A858-D728B93340E4}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -525,15 +526,16 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3462184</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>2812480</v>
+      </c>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -541,7 +543,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -549,16 +551,16 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5">
-        <f>0.022*4020</f>
-        <v>88.44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <f>B2*0.02</f>
+        <v>56249.599999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -566,7 +568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -575,16 +577,15 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>15</v>
       </c>
       <c r="B8">
-        <f>1320 * 4.02</f>
-        <v>5306.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+        <v>5280</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
